--- a/students.xlsx
+++ b/students.xlsx
@@ -8,24 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\test\exam sit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177CC922-2B9F-4877-A96C-8C8D6CD66B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F6D957-FEB5-467C-85C6-405A7874F797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="87">
   <si>
     <t>اسم الطالب</t>
   </si>
@@ -121,6 +130,171 @@
   </si>
   <si>
     <t>أ</t>
+  </si>
+  <si>
+    <t>ادهم مشتاق احمد صالح</t>
+  </si>
+  <si>
+    <t>امير محي محمد عبد</t>
+  </si>
+  <si>
+    <t>انس أكرم هاشم محمد</t>
+  </si>
+  <si>
+    <t>انمار خالد جبير عايش</t>
+  </si>
+  <si>
+    <t>ايهم ابراهيم احمد بطاح</t>
+  </si>
+  <si>
+    <t>خطاب عامر مشرف خزعل</t>
+  </si>
+  <si>
+    <t>رواد احمد كردي ابراهيم</t>
+  </si>
+  <si>
+    <t>سمير محي محمد عبد</t>
+  </si>
+  <si>
+    <t>عباس وسام عدنان محمد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عبد الرحمن جمعه ثرثار مخلف </t>
+  </si>
+  <si>
+    <t>عبد الرحمن عمار حمود جاسم</t>
+  </si>
+  <si>
+    <t>عبد الرحمن محمد مشرف عطاالله</t>
+  </si>
+  <si>
+    <t>عبدالله عبد الباسط وهيب محمد</t>
+  </si>
+  <si>
+    <t>علي اياد هاشم محمد</t>
+  </si>
+  <si>
+    <t>عمر اياد احمد رزيج</t>
+  </si>
+  <si>
+    <t>عمر مهند عليوي سليمان</t>
+  </si>
+  <si>
+    <t>محمد جاسم محمد بستان</t>
+  </si>
+  <si>
+    <t>محمد صدام محمد فريح</t>
+  </si>
+  <si>
+    <t>محمد هلال خلف جدوع</t>
+  </si>
+  <si>
+    <t>مصطفى جسام محمد علي</t>
+  </si>
+  <si>
+    <t>مصطفى ساجد علي محيسن</t>
+  </si>
+  <si>
+    <t>مصطفى عدي عدنان عبد</t>
+  </si>
+  <si>
+    <t>يعقوب رياض عايد حمد</t>
+  </si>
+  <si>
+    <t>يوسف احمد فاضل حسن</t>
+  </si>
+  <si>
+    <t>الخامس</t>
+  </si>
+  <si>
+    <t>احمد ساجد علي محيسن</t>
+  </si>
+  <si>
+    <t>احمد فواد جمار نشمي</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد محمد</t>
+  </si>
+  <si>
+    <t>انس إبراهيم حميد مهيدي</t>
+  </si>
+  <si>
+    <t>ايمن عمر ابراهيم غزاي</t>
+  </si>
+  <si>
+    <t>تيسير محمد جاسم محمد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ثامر عامر مشرف خزعل </t>
+  </si>
+  <si>
+    <t>حسام باسم محمد عبد</t>
+  </si>
+  <si>
+    <t>حسام هلال ثرثار مخلف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حسين علي نصيف جسام </t>
+  </si>
+  <si>
+    <t xml:space="preserve">عباس علي نصيف جسام </t>
+  </si>
+  <si>
+    <t>عبد الرحمن صفاء ابراهيم غزاي</t>
+  </si>
+  <si>
+    <t>علي محمد احمد محمد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عمر ثامر احمد خلف </t>
+  </si>
+  <si>
+    <t>عيسى جاسم حامد حمادي</t>
+  </si>
+  <si>
+    <t>مثنى حماد علي عيد</t>
+  </si>
+  <si>
+    <t>محمد باسم محمد خضير</t>
+  </si>
+  <si>
+    <t>محمد علي مخيف احمد</t>
+  </si>
+  <si>
+    <t>محمد غزاي كاظم فرحان</t>
+  </si>
+  <si>
+    <t>محمد محمود حمد عبد</t>
+  </si>
+  <si>
+    <t>محمد نزار عايد حمد</t>
+  </si>
+  <si>
+    <t>محمود محمد كريم ثميل</t>
+  </si>
+  <si>
+    <t>منتظر عبد الستار حماد رزيج</t>
+  </si>
+  <si>
+    <t>موسى عامر احمد خلف</t>
+  </si>
+  <si>
+    <t>نشأت اكرم احميد حماد</t>
+  </si>
+  <si>
+    <t>وسيم محمد اوهيب محمد</t>
+  </si>
+  <si>
+    <t>ياسر احمد علي احمد</t>
+  </si>
+  <si>
+    <t>يوسف حسام احمد خلف</t>
+  </si>
+  <si>
+    <t>يونس سعد هلال دبيس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الرابع </t>
   </si>
 </sst>
 </file>
@@ -176,8 +350,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DEF5069-4E76-455F-8E41-E65A12D85979}" name="Table1" displayName="Table1" ref="A1:C28" totalsRowShown="0">
-  <autoFilter ref="A1:C28" xr:uid="{8DEF5069-4E76-455F-8E41-E65A12D85979}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8DEF5069-4E76-455F-8E41-E65A12D85979}" name="Table1" displayName="Table1" ref="A1:C81" totalsRowShown="0">
+  <autoFilter ref="A1:C81" xr:uid="{8DEF5069-4E76-455F-8E41-E65A12D85979}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{A6781618-9DEE-4B50-897F-67369A7CCC2A}" name="اسم الطالب"/>
     <tableColumn id="2" xr3:uid="{F1B12BE0-8C79-4846-B41D-04A52D5F7014}" name="المرحلة "/>
@@ -450,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -766,6 +940,589 @@
         <v>31</v>
       </c>
     </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" t="s">
+        <v>86</v>
+      </c>
+      <c r="C53" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" t="s">
+        <v>86</v>
+      </c>
+      <c r="C56" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" t="s">
+        <v>86</v>
+      </c>
+      <c r="C57" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" t="s">
+        <v>86</v>
+      </c>
+      <c r="C58" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" t="s">
+        <v>86</v>
+      </c>
+      <c r="C59" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" t="s">
+        <v>86</v>
+      </c>
+      <c r="C60" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" t="s">
+        <v>86</v>
+      </c>
+      <c r="C61" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" t="s">
+        <v>86</v>
+      </c>
+      <c r="C62" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" t="s">
+        <v>86</v>
+      </c>
+      <c r="C63" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" t="s">
+        <v>86</v>
+      </c>
+      <c r="C64" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" t="s">
+        <v>86</v>
+      </c>
+      <c r="C65" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66" t="s">
+        <v>86</v>
+      </c>
+      <c r="C66" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" t="s">
+        <v>86</v>
+      </c>
+      <c r="C67" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" t="s">
+        <v>86</v>
+      </c>
+      <c r="C68" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" t="s">
+        <v>86</v>
+      </c>
+      <c r="C69" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" t="s">
+        <v>86</v>
+      </c>
+      <c r="C70" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" t="s">
+        <v>86</v>
+      </c>
+      <c r="C71" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C72" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" t="s">
+        <v>86</v>
+      </c>
+      <c r="C73" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" t="s">
+        <v>86</v>
+      </c>
+      <c r="C74" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" t="s">
+        <v>86</v>
+      </c>
+      <c r="C75" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" t="s">
+        <v>86</v>
+      </c>
+      <c r="C76" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" t="s">
+        <v>86</v>
+      </c>
+      <c r="C77" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" t="s">
+        <v>86</v>
+      </c>
+      <c r="C78" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79" t="s">
+        <v>86</v>
+      </c>
+      <c r="C79" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81" t="s">
+        <v>86</v>
+      </c>
+      <c r="C81" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
